--- a/assets/Warehouse & Sorting Locations.xlsx
+++ b/assets/Warehouse & Sorting Locations.xlsx
@@ -5,18 +5,18 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://teamsite.maerskgroup.com/teams/VSCMTransportationVisibleSCMMigrated/Shared Documents/04. Pricing/E-Delivery Pricing/1. Pricing Tools/1. OPAA App/References/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GMO143\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="122" documentId="8_{E4346982-C8D2-4F5A-BDE3-FCC1547C089D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7EABE45-6D6E-4D96-9819-C81907759784}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{561B2240-05D3-4DA5-8B1C-B7EABD4647E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{A0AC1BA6-0124-4D90-B4EC-DAACD076735D}"/>
+    <workbookView xWindow="2640" yWindow="2640" windowWidth="38700" windowHeight="15345" xr2:uid="{A0AC1BA6-0124-4D90-B4EC-DAACD076735D}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse &amp; Sort Locations" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Warehouse &amp; Sort Locations'!$A$1:$G$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Warehouse &amp; Sort Locations'!$A$1:$H$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="109" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
   <si>
     <t>Building Name</t>
   </si>
@@ -267,6 +267,15 @@
   </si>
   <si>
     <t>FastTrack DFW</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Sort</t>
+  </si>
+  <si>
+    <t>Warehouse</t>
   </si>
 </sst>
 </file>
@@ -725,17 +734,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BFCA06-95E4-4D71-BAFD-1E8652E657DD}">
-  <dimension ref="A1:I17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="2" width="12.54296875" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="53.81640625" customWidth="1"/>
-    <col min="7" max="7" width="17.453125" customWidth="1"/>
+    <col min="2" max="3" width="12.5703125" customWidth="1"/>
+    <col min="4" max="4" width="16" customWidth="1"/>
+    <col min="5" max="5" width="53.85546875" customWidth="1"/>
+    <col min="8" max="8" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -743,28 +752,31 @@
         <v>12</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
@@ -772,28 +784,31 @@
         <v>13</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="E2" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="E2" s="5">
+      <c r="F2" s="5">
         <v>84128</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="9" t="s">
+      <c r="H2" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="9">
+      <c r="I2" s="9">
         <v>40.718688595319598</v>
       </c>
-      <c r="I2" s="9">
+      <c r="J2" s="9">
         <v>-112.050019228366</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>10</v>
       </c>
@@ -801,57 +816,63 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="E3" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="E3" s="5">
+      <c r="F3" s="5">
         <v>30213</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="G3" s="9" t="s">
+      <c r="H3" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="H3" s="9">
+      <c r="I3" s="9">
         <v>33.598599999999998</v>
       </c>
-      <c r="I3" s="9">
+      <c r="J3" s="9">
         <v>-84.582099999999997</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="E4" s="11" t="s">
         <v>65</v>
       </c>
-      <c r="E4" s="7">
+      <c r="F4" s="7">
         <v>45069</v>
       </c>
-      <c r="F4" s="8" t="s">
+      <c r="G4" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="H4" s="4">
+      <c r="I4" s="4">
         <v>39.353999999999999</v>
       </c>
-      <c r="I4" s="4">
+      <c r="J4" s="4">
         <v>-84.364699999999999</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
@@ -859,28 +880,31 @@
         <v>13</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="11" t="s">
+      <c r="E5" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <v>92374</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="G5" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="9">
+      <c r="I5" s="9">
         <v>34.055999999999997</v>
       </c>
-      <c r="I5" s="9">
+      <c r="J5" s="9">
         <v>-117.2079</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -888,28 +912,31 @@
         <v>13</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <v>91752</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H6" s="9">
+      <c r="I6" s="9">
         <v>33.978999999999999</v>
       </c>
-      <c r="I6" s="9">
+      <c r="J6" s="9">
         <v>-117.55419999999999</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -917,28 +944,31 @@
         <v>13</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="12" t="s">
+      <c r="E7" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="F7" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="G7" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H7" s="9">
+      <c r="I7" s="9">
         <v>33.982999999999997</v>
       </c>
-      <c r="I7" s="9">
+      <c r="J7" s="9">
         <v>-117.688</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>1</v>
       </c>
@@ -946,28 +976,31 @@
         <v>13</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="E8" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="E8" s="5">
+      <c r="F8" s="5">
         <v>8016</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="9">
+      <c r="I8" s="9">
         <v>40.061</v>
       </c>
-      <c r="I8" s="9">
+      <c r="J8" s="9">
         <v>-74.842100000000002</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>2</v>
       </c>
@@ -975,28 +1008,31 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="E9" s="10" t="s">
         <v>60</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>31419</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="G9" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="H9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H9" s="10">
+      <c r="I9" s="10">
         <v>32.126600000000003</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="J9" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>3</v>
       </c>
@@ -1004,28 +1040,31 @@
         <v>13</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="E10" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="E10" s="2">
+      <c r="F10" s="2">
         <v>43125</v>
       </c>
-      <c r="F10" s="10" t="s">
+      <c r="G10" s="10" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="10" t="s">
+      <c r="H10" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H10" s="10">
+      <c r="I10" s="10">
         <v>39.838262176685802</v>
       </c>
-      <c r="I10" s="10">
+      <c r="J10" s="10">
         <v>-82.921309182516495</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>4</v>
       </c>
@@ -1033,28 +1072,31 @@
         <v>13</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="11" t="s">
+      <c r="E11" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="F11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="G11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="G11" s="9" t="s">
+      <c r="H11" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="H11" s="9">
+      <c r="I11" s="9">
         <v>43.771799999999999</v>
       </c>
-      <c r="I11" s="9">
+      <c r="J11" s="9">
         <v>-79.858000000000004</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>5</v>
       </c>
@@ -1062,28 +1104,31 @@
         <v>13</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="D12" s="13" t="s">
+      <c r="E12" s="13" t="s">
         <v>58</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="F12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="G12" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="H12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="H12" s="9">
+      <c r="I12" s="9">
         <v>49.182499999999997</v>
       </c>
-      <c r="I12" s="9">
+      <c r="J12" s="9">
         <v>-123.068</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>67</v>
       </c>
@@ -1091,28 +1136,31 @@
         <v>70</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="D13" s="11" t="s">
+      <c r="E13" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="E13" s="5">
+      <c r="F13" s="5">
         <v>11413</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="G13" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="H13" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="H13" s="9">
+      <c r="I13" s="9">
         <v>40.652281655806199</v>
       </c>
-      <c r="I13" s="9">
+      <c r="J13" s="9">
         <v>-73.758001299768097</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>69</v>
       </c>
@@ -1120,28 +1168,31 @@
         <v>70</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="E14" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E14" s="5">
+      <c r="F14" s="5">
         <v>7008</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="H14" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="H14" s="9">
+      <c r="I14" s="9">
         <v>40.582500000000003</v>
       </c>
-      <c r="I14" s="9">
+      <c r="J14" s="9">
         <v>-74.228099999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>74</v>
       </c>
@@ -1149,28 +1200,31 @@
         <v>13</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="11" t="s">
+      <c r="E15" s="11" t="s">
         <v>71</v>
       </c>
-      <c r="E15" s="5">
+      <c r="F15" s="5">
         <v>90220</v>
       </c>
-      <c r="F15" s="6" t="s">
+      <c r="G15" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="H15" s="9">
+      <c r="I15" s="9">
         <v>33.862487020519097</v>
       </c>
-      <c r="I15" s="9">
+      <c r="J15" s="9">
         <v>-118.22728165347</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -1178,28 +1232,31 @@
         <v>70</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E16" s="5">
+      <c r="F16" s="5">
         <v>60191</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="G16" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="H16" s="9">
+      <c r="I16" s="9">
         <v>41.975999999999999</v>
       </c>
-      <c r="I16" s="9">
+      <c r="J16" s="9">
         <v>-87.940100000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>75</v>
       </c>
@@ -1207,24 +1264,27 @@
         <v>70</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="E17" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="E17" s="5">
+      <c r="F17" s="5">
         <v>76051</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="G17" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="9">
+      <c r="I17" s="9">
         <v>32.897500000000001</v>
       </c>
-      <c r="I17" s="9">
+      <c r="J17" s="9">
         <v>-97.049599999999998</v>
       </c>
     </row>
@@ -1238,23 +1298,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <FileStatus xmlns="07046c96-ba5b-4543-b286-c3b0b494e77d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004155A60613941B44A7FF777A442D62C2" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22b820f861d1dd5d7d0a4345cf85a231">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c05411ed-81b0-4e9b-981a-7ee4d002c10a" xmlns:ns3="07046c96-ba5b-4543-b286-c3b0b494e77d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3e9c26db3523b1d6e9b3cee19d309f7a" ns2:_="" ns3:_="">
     <xsd:import namespace="c05411ed-81b0-4e9b-981a-7ee4d002c10a"/>
@@ -1469,25 +1512,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{480FC467-89FB-41B9-801A-6B5CE72AB4A9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="07046c96-ba5b-4543-b286-c3b0b494e77d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADE8DDF-68BB-4719-AD08-39FD3A8414AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <FileStatus xmlns="07046c96-ba5b-4543-b286-c3b0b494e77d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A76B69C8-573C-4351-8F00-F3AE16DDF65B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1504,4 +1546,22 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADE8DDF-68BB-4719-AD08-39FD3A8414AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{480FC467-89FB-41B9-801A-6B5CE72AB4A9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="07046c96-ba5b-4543-b286-c3b0b494e77d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/assets/Warehouse & Sorting Locations.xlsx
+++ b/assets/Warehouse & Sorting Locations.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GMO143\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{561B2240-05D3-4DA5-8B1C-B7EABD4647E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD03CCB6-DEE8-47E3-956C-1BEFBC0C33F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2640" yWindow="2640" windowWidth="38700" windowHeight="15345" xr2:uid="{A0AC1BA6-0124-4D90-B4EC-DAACD076735D}"/>
+    <workbookView xWindow="2985" yWindow="2985" windowWidth="38700" windowHeight="15345" xr2:uid="{A0AC1BA6-0124-4D90-B4EC-DAACD076735D}"/>
   </bookViews>
   <sheets>
     <sheet name="Warehouse &amp; Sort Locations" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="69">
   <si>
     <t>Building Name</t>
   </si>
@@ -53,12 +53,6 @@
     <t>Maersk Groveport</t>
   </si>
   <si>
-    <t>Maersk Toronto</t>
-  </si>
-  <si>
-    <t>Maersk Vancouver</t>
-  </si>
-  <si>
     <t>Maersk Chino</t>
   </si>
   <si>
@@ -110,12 +104,6 @@
     <t>Groveport</t>
   </si>
   <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>Vancouver</t>
-  </si>
-  <si>
     <t>Address</t>
   </si>
   <si>
@@ -173,21 +161,6 @@
     <t xml:space="preserve">NJ​ </t>
   </si>
   <si>
-    <t>12333 Airport Road, Caledon, ON, L7C 2X3 Canada</t>
-  </si>
-  <si>
-    <t>L7C 2X3</t>
-  </si>
-  <si>
-    <t>ON</t>
-  </si>
-  <si>
-    <t>V4G 1B5</t>
-  </si>
-  <si>
-    <t>BC</t>
-  </si>
-  <si>
     <t>NY</t>
   </si>
   <si>
@@ -213,9 +186,6 @@
   </si>
   <si>
     <t>TX</t>
-  </si>
-  <si>
-    <t>8400 River Road Delta, BC V4G 1B5</t>
   </si>
   <si>
     <t>Grapeville</t>
@@ -734,7 +704,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21BFCA06-95E4-4D71-BAFD-1E8652E657DD}">
-  <dimension ref="A1:J17"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
@@ -749,57 +719,57 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>15</v>
-      </c>
       <c r="E2" s="11" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F2" s="5">
         <v>84128</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="H2" s="9" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="I2" s="9">
         <v>40.718688595319598</v>
@@ -810,28 +780,28 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E3" s="11" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="F3" s="5">
         <v>30213</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I3" s="9">
         <v>33.598599999999998</v>
@@ -842,28 +812,28 @@
     </row>
     <row r="4" spans="1:10" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F4" s="7">
         <v>45069</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I4" s="4">
         <v>39.353999999999999</v>
@@ -874,28 +844,28 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="F5" s="5">
         <v>92374</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H5" s="9" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I5" s="9">
         <v>34.055999999999997</v>
@@ -906,28 +876,28 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="F6" s="5">
         <v>91752</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="I6" s="9">
         <v>33.978999999999999</v>
@@ -938,28 +908,28 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I7" s="9">
         <v>33.982999999999997</v>
@@ -973,25 +943,25 @@
         <v>1</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="F8" s="5">
         <v>8016</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="I8" s="9">
         <v>40.061</v>
@@ -1005,31 +975,31 @@
         <v>2</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F9" s="2">
         <v>31419</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H9" s="10" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="I9" s="10">
         <v>32.126600000000003</v>
       </c>
       <c r="J9" s="10" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
@@ -1037,25 +1007,25 @@
         <v>3</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2">
         <v>43125</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H10" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="I10" s="10">
         <v>39.838262176685802</v>
@@ -1066,225 +1036,161 @@
     </row>
     <row r="11" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>4</v>
+        <v>57</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>23</v>
+        <v>57</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>45</v>
+        <v>58</v>
+      </c>
+      <c r="F11" s="5">
+        <v>11413</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I11" s="9">
-        <v>43.771799999999999</v>
+        <v>40.652281655806199</v>
       </c>
       <c r="J11" s="9">
-        <v>-79.858000000000004</v>
+        <v>-73.758001299768097</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E12" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>47</v>
+        <v>59</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="5">
+        <v>7008</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="I12" s="9">
-        <v>49.182499999999997</v>
+        <v>40.582500000000003</v>
       </c>
       <c r="J12" s="9">
-        <v>-123.068</v>
+        <v>-74.228099999999998</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>77</v>
-      </c>
       <c r="D13" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="F13" s="5">
-        <v>11413</v>
+        <v>90220</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="I13" s="9">
-        <v>40.652281655806199</v>
+        <v>33.862487020519097</v>
       </c>
       <c r="J13" s="9">
-        <v>-73.758001299768097</v>
+        <v>-118.22728165347</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>51</v>
+        <v>63</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>44</v>
       </c>
       <c r="F14" s="5">
-        <v>7008</v>
+        <v>60191</v>
       </c>
       <c r="G14" s="6" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>52</v>
+        <v>46</v>
       </c>
       <c r="I14" s="9">
-        <v>40.582500000000003</v>
+        <v>41.975999999999999</v>
       </c>
       <c r="J14" s="9">
-        <v>-74.228099999999998</v>
+        <v>-87.940100000000001</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>13</v>
+        <v>60</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="E15" s="14" t="s">
+        <v>47</v>
       </c>
       <c r="F15" s="5">
-        <v>90220</v>
+        <v>76051</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>72</v>
+        <v>49</v>
       </c>
       <c r="I15" s="9">
-        <v>33.862487020519097</v>
+        <v>32.897500000000001</v>
       </c>
       <c r="J15" s="9">
-        <v>-118.22728165347</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="5">
-        <v>60191</v>
-      </c>
-      <c r="G16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="H16" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="I16" s="9">
-        <v>41.975999999999999</v>
-      </c>
-      <c r="J16" s="9">
-        <v>-87.940100000000001</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E17" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="5">
-        <v>76051</v>
-      </c>
-      <c r="G17" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="H17" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="I17" s="9">
-        <v>32.897500000000001</v>
-      </c>
-      <c r="J17" s="9">
         <v>-97.049599999999998</v>
       </c>
     </row>
@@ -1298,6 +1204,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <FileStatus xmlns="07046c96-ba5b-4543-b286-c3b0b494e77d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101004155A60613941B44A7FF777A442D62C2" ma:contentTypeVersion="13" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="22b820f861d1dd5d7d0a4345cf85a231">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="c05411ed-81b0-4e9b-981a-7ee4d002c10a" xmlns:ns3="07046c96-ba5b-4543-b286-c3b0b494e77d" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3e9c26db3523b1d6e9b3cee19d309f7a" ns2:_="" ns3:_="">
     <xsd:import namespace="c05411ed-81b0-4e9b-981a-7ee4d002c10a"/>
@@ -1512,24 +1435,25 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{480FC467-89FB-41B9-801A-6B5CE72AB4A9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="07046c96-ba5b-4543-b286-c3b0b494e77d"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <FileStatus xmlns="07046c96-ba5b-4543-b286-c3b0b494e77d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADE8DDF-68BB-4719-AD08-39FD3A8414AD}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A76B69C8-573C-4351-8F00-F3AE16DDF65B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1546,22 +1470,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EADE8DDF-68BB-4719-AD08-39FD3A8414AD}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{480FC467-89FB-41B9-801A-6B5CE72AB4A9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="07046c96-ba5b-4543-b286-c3b0b494e77d"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>